--- a/GF_X-master/AAAGameData/DataTables/Level1SettingTable.xlsx
+++ b/GF_X-master/AAAGameData/DataTables/Level1SettingTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowHeight="17925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -143,19 +143,19 @@
     <t>阶段分数</t>
   </si>
   <si>
-    <t>1,50;0.5,25;2;25</t>
-  </si>
-  <si>
-    <t>1,50;0.5,25;2;26</t>
-  </si>
-  <si>
-    <t>1,50;0.5,25;2;27</t>
-  </si>
-  <si>
-    <t>1,50;0.5,25;2;28</t>
-  </si>
-  <si>
-    <t>1,50;0.5,25;2;29</t>
+    <t>1,50;0.5,25;2,25</t>
+  </si>
+  <si>
+    <t>1,50;0.5,25;2,26</t>
+  </si>
+  <si>
+    <t>1,50;0.5,25;2,27</t>
+  </si>
+  <si>
+    <t>1,50;0.5,25;2,28</t>
+  </si>
+  <si>
+    <t>1,50;0.5,25;2,29</t>
   </si>
 </sst>
 </file>
@@ -1326,16 +1326,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:W9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="8" max="8" width="19.7777777777778" customWidth="1"/>
-    <col min="9" max="9" width="21.4444444444444" customWidth="1"/>
-    <col min="10" max="10" width="19.8888888888889" customWidth="1"/>
-    <col min="11" max="11" width="21.5555555555556" customWidth="1"/>
-    <col min="12" max="12" width="20.1111111111111" customWidth="1"/>
-    <col min="13" max="13" width="21.7777777777778" customWidth="1"/>
-    <col min="14" max="14" width="20.1111111111111" customWidth="1"/>
+    <col min="8" max="8" width="19.7809523809524" customWidth="1"/>
+    <col min="9" max="9" width="21.447619047619" customWidth="1"/>
+    <col min="10" max="10" width="19.8857142857143" customWidth="1"/>
+    <col min="11" max="11" width="21.552380952381" customWidth="1"/>
+    <col min="12" max="12" width="20.1142857142857" customWidth="1"/>
+    <col min="13" max="13" width="21.7809523809524" customWidth="1"/>
+    <col min="14" max="14" width="20.1142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1819,17 +1819,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="2:2">
-      <c r="B10">
-        <v>6</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="D1:G1 H1:I1 J1 K1 L1:W1 X1:Y1">
+    <dataValidation type="list" allowBlank="1" sqref="D1:Y1">
       <formula1>"i18n"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D3:G3 H3:I3 J3:K3 L3:M3 N3:W3 X3:Y3">
+    <dataValidation type="list" sqref="D3:Y3">
       <formula1>"int,bool,enum,double,string[],string,float,uint,short,Vector4,Vector2,Vector3Int,Vector3,Color,Color32,Vector3[],Vector2Int,int[],float[],bool[],double[],ushort,ulong,int[][],double[][],decimal,long,float[][],bool[][],Rect,Quaternion,DateTime,sbyte,char"</formula1>
     </dataValidation>
   </dataValidations>

--- a/GF_X-master/AAAGameData/DataTables/Level1SettingTable.xlsx
+++ b/GF_X-master/AAAGameData/DataTables/Level1SettingTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17925"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -143,19 +143,19 @@
     <t>阶段分数</t>
   </si>
   <si>
-    <t>1,50;0.5,25;2,25</t>
-  </si>
-  <si>
-    <t>1,50;0.5,25;2,26</t>
-  </si>
-  <si>
-    <t>1,50;0.5,25;2,27</t>
-  </si>
-  <si>
-    <t>1,50;0.5,25;2,28</t>
-  </si>
-  <si>
-    <t>1,50;0.5,25;2,29</t>
+    <t>[1,50],[0.5,25],[2,25]</t>
+  </si>
+  <si>
+    <t>[1,50],[0.5,25],[2,26]</t>
+  </si>
+  <si>
+    <t>[1,50],[0.5,25],[2,27]</t>
+  </si>
+  <si>
+    <t>[1,50],[0.5,25],[2,28]</t>
+  </si>
+  <si>
+    <t>[1,50],[0.5,25],[2,29]</t>
   </si>
 </sst>
 </file>

--- a/GF_X-master/AAAGameData/DataTables/Level1SettingTable.xlsx
+++ b/GF_X-master/AAAGameData/DataTables/Level1SettingTable.xlsx
@@ -331,12 +331,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1588,10 +1588,10 @@
         <v>61</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="N6" t="s">
         <v>28</v>

--- a/GF_X-master/AAAGameData/DataTables/Level1SettingTable.xlsx
+++ b/GF_X-master/AAAGameData/DataTables/Level1SettingTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="48">
   <si>
     <t>#</t>
   </si>
@@ -141,6 +141,77 @@
   </si>
   <si>
     <t>阶段分数</t>
+  </si>
+  <si>
+    <t>点击分数/点击</t>
+  </si>
+  <si>
+    <t>长按分数/帧</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>损失分数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>帧</t>
+    </r>
+  </si>
+  <si>
+    <t>来电固定间隔时间判定来电间隔判定概率</t>
+  </si>
+  <si>
+    <t>挂断固定间隔时间判定挂断电话判定概率</t>
+  </si>
+  <si>
+    <t>敲门判定间隔时间</t>
+  </si>
+  <si>
+    <t>触发敲门判定概率</t>
+  </si>
+  <si>
+    <t>撤离预告时间与概率</t>
+  </si>
+  <si>
+    <t>开门事件概率</t>
+  </si>
+  <si>
+    <t>敌人生命值</t>
+  </si>
+  <si>
+    <t>敌人移动时间</t>
+  </si>
+  <si>
+    <t>敌人伤害</t>
+  </si>
+  <si>
+    <t>间隔判定时间</t>
+  </si>
+  <si>
+    <t>触发概率</t>
+  </si>
+  <si>
+    <t>关窗判定时间</t>
+  </si>
+  <si>
+    <t>关窗触发概率</t>
   </si>
   <si>
     <t>[1,50],[0.5,25],[2,25]</t>
@@ -331,12 +402,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1327,15 +1398,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:W9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="8" max="8" width="19.7809523809524" customWidth="1"/>
-    <col min="9" max="9" width="21.447619047619" customWidth="1"/>
-    <col min="10" max="10" width="19.8857142857143" customWidth="1"/>
-    <col min="11" max="11" width="21.552380952381" customWidth="1"/>
-    <col min="12" max="12" width="20.1142857142857" customWidth="1"/>
-    <col min="13" max="13" width="21.7809523809524" customWidth="1"/>
-    <col min="14" max="14" width="20.1142857142857" customWidth="1"/>
+    <col min="8" max="8" width="19.7777777777778" customWidth="1"/>
+    <col min="9" max="9" width="21.4444444444444" customWidth="1"/>
+    <col min="10" max="10" width="19.8888888888889" customWidth="1"/>
+    <col min="11" max="11" width="21.5555555555556" customWidth="1"/>
+    <col min="12" max="12" width="20.1111111111111" customWidth="1"/>
+    <col min="13" max="13" width="21.7777777777778" customWidth="1"/>
+    <col min="14" max="14" width="20.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1479,7 +1550,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:22">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -1492,20 +1563,67 @@
       <c r="D4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="5" spans="2:23">
+    <row r="5" spans="2:22">
       <c r="B5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>100</v>
+        <v>2400</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1529,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -1541,7 +1659,7 @@
         <v>0</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1555,149 +1673,140 @@
       <c r="V5">
         <v>0</v>
       </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" spans="2:23">
+    <row r="6" spans="2:22">
       <c r="B6">
         <v>2</v>
       </c>
       <c r="D6">
-        <v>200</v>
+        <v>4800</v>
       </c>
       <c r="E6">
+        <v>20</v>
+      </c>
+      <c r="F6">
         <v>4</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L6">
         <v>2</v>
       </c>
       <c r="M6">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N6" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="O6">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="P6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="S6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>1</v>
-      </c>
-      <c r="W6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:23">
+    <row r="7" spans="2:22">
       <c r="B7">
         <v>3</v>
       </c>
       <c r="D7">
-        <v>400</v>
+        <v>9600</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G7">
         <v>2</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K7">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L7">
         <v>2</v>
       </c>
       <c r="M7">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="N7" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="O7">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="P7">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q7">
         <v>2</v>
       </c>
       <c r="R7">
-        <v>2</v>
+        <v>4000</v>
       </c>
       <c r="S7">
         <v>2</v>
       </c>
       <c r="T7">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="U7">
         <v>2</v>
       </c>
       <c r="V7">
-        <v>2</v>
-      </c>
-      <c r="W7">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
-    <row r="8" spans="2:23">
+    <row r="8" spans="2:22">
       <c r="B8">
         <v>4</v>
       </c>
       <c r="D8">
-        <v>800</v>
+        <v>19200</v>
       </c>
       <c r="E8">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="F8">
         <v>8</v>
@@ -1706,117 +1815,111 @@
         <v>3</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I8">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K8">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M8">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="N8" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="O8">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="P8">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="Q8">
         <v>3</v>
       </c>
       <c r="R8">
-        <v>3</v>
+        <v>8000</v>
       </c>
       <c r="S8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T8">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="U8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V8">
-        <v>3</v>
-      </c>
-      <c r="W8">
-        <v>3</v>
+        <v>50</v>
       </c>
     </row>
-    <row r="9" spans="2:23">
+    <row r="9" spans="2:22">
       <c r="B9">
         <v>5</v>
       </c>
       <c r="D9">
-        <v>950</v>
+        <v>38400</v>
       </c>
       <c r="E9">
-        <v>32</v>
+        <v>160</v>
       </c>
       <c r="F9">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>4</v>
       </c>
       <c r="H9">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I9">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="J9">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K9">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="L9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M9">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="N9" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="O9">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="P9">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="Q9">
         <v>4</v>
       </c>
       <c r="R9">
-        <v>4</v>
+        <v>16000</v>
       </c>
       <c r="S9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T9">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="U9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V9">
-        <v>4</v>
-      </c>
-      <c r="W9">
-        <v>4</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/GF_X-master/AAAGameData/DataTables/Level1SettingTable.xlsx
+++ b/GF_X-master/AAAGameData/DataTables/Level1SettingTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -1398,15 +1398,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:W9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="8" max="8" width="19.7777777777778" customWidth="1"/>
-    <col min="9" max="9" width="21.4444444444444" customWidth="1"/>
-    <col min="10" max="10" width="19.8888888888889" customWidth="1"/>
-    <col min="11" max="11" width="21.5555555555556" customWidth="1"/>
-    <col min="12" max="12" width="20.1111111111111" customWidth="1"/>
-    <col min="13" max="13" width="21.7777777777778" customWidth="1"/>
-    <col min="14" max="14" width="20.1111111111111" customWidth="1"/>
+    <col min="8" max="8" width="19.7809523809524" customWidth="1"/>
+    <col min="9" max="9" width="21.447619047619" customWidth="1"/>
+    <col min="10" max="10" width="19.8857142857143" customWidth="1"/>
+    <col min="11" max="11" width="21.552380952381" customWidth="1"/>
+    <col min="12" max="12" width="20.1142857142857" customWidth="1"/>
+    <col min="13" max="13" width="21.7809523809524" customWidth="1"/>
+    <col min="14" max="14" width="20.1142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1641,16 +1641,16 @@
         <v>60</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N5" t="s">
         <v>43</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -1706,7 +1706,7 @@
         <v>2</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N6" t="s">
         <v>44</v>

--- a/GF_X-master/AAAGameData/DataTables/Level1SettingTable.xlsx
+++ b/GF_X-master/AAAGameData/DataTables/Level1SettingTable.xlsx
@@ -1406,7 +1406,8 @@
     <col min="11" max="11" width="21.552380952381" customWidth="1"/>
     <col min="12" max="12" width="20.1142857142857" customWidth="1"/>
     <col min="13" max="13" width="21.7809523809524" customWidth="1"/>
-    <col min="14" max="14" width="20.1142857142857" customWidth="1"/>
+    <col min="14" max="14" width="17.4285714285714" customWidth="1"/>
+    <col min="15" max="15" width="20.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1650,13 +1651,13 @@
         <v>43</v>
       </c>
       <c r="O5">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R5">
         <v>1000</v>

--- a/GF_X-master/AAAGameData/DataTables/Level1SettingTable.xlsx
+++ b/GF_X-master/AAAGameData/DataTables/Level1SettingTable.xlsx
@@ -1645,19 +1645,19 @@
         <v>2</v>
       </c>
       <c r="M5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N5" t="s">
         <v>43</v>
       </c>
       <c r="O5">
+        <v>100</v>
+      </c>
+      <c r="P5">
         <v>0</v>
       </c>
-      <c r="P5">
-        <v>10</v>
-      </c>
       <c r="Q5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R5">
         <v>1000</v>
@@ -1707,7 +1707,7 @@
         <v>2</v>
       </c>
       <c r="M6">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N6" t="s">
         <v>44</v>

--- a/GF_X-master/AAAGameData/DataTables/Level1SettingTable.xlsx
+++ b/GF_X-master/AAAGameData/DataTables/Level1SettingTable.xlsx
@@ -55,12 +55,81 @@
         </r>
       </text>
     </comment>
+    <comment ref="O2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>susum:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+预告时间,该预告时间的权重
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>susum:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+预告时间,该预告时间的权重
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>susum:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+预告时间,该预告时间的权重
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="55">
   <si>
     <t>#</t>
   </si>
@@ -101,6 +170,9 @@
     <t>Event_Door_OpenProp</t>
   </si>
   <si>
+    <t>Event_Door_Time</t>
+  </si>
+  <si>
     <t>Event_Door_PreTime</t>
   </si>
   <si>
@@ -122,10 +194,13 @@
     <t>Event_Windows_OpenProp</t>
   </si>
   <si>
-    <t>Event_Windows_CloseCD</t>
-  </si>
-  <si>
-    <t>Event_Windows_CloseProp</t>
+    <t>Event_Window_Time</t>
+  </si>
+  <si>
+    <t>Event_Window_PreTime</t>
+  </si>
+  <si>
+    <t>Event_Window_TypeProp</t>
   </si>
   <si>
     <t>int</t>
@@ -187,6 +262,9 @@
     <t>触发敲门判定概率</t>
   </si>
   <si>
+    <t>持续时间与概率</t>
+  </si>
+  <si>
     <t>撤离预告时间与概率</t>
   </si>
   <si>
@@ -208,22 +286,34 @@
     <t>触发概率</t>
   </si>
   <si>
-    <t>关窗判定时间</t>
-  </si>
-  <si>
-    <t>关窗触发概率</t>
+    <t>开窗事件概率</t>
+  </si>
+  <si>
+    <t>[2,50],[3,25],[4,25]</t>
   </si>
   <si>
     <t>[1,50],[0.5,25],[2,25]</t>
   </si>
   <si>
+    <t>[2,50],[3,25],[4,26]</t>
+  </si>
+  <si>
     <t>[1,50],[0.5,25],[2,26]</t>
   </si>
   <si>
+    <t>[2,50],[3,25],[4,27]</t>
+  </si>
+  <si>
     <t>[1,50],[0.5,25],[2,27]</t>
   </si>
   <si>
+    <t>[2,50],[3,25],[4,28]</t>
+  </si>
+  <si>
     <t>[1,50],[0.5,25],[2,28]</t>
+  </si>
+  <si>
+    <t>[2,50],[3,25],[4,29]</t>
   </si>
   <si>
     <t>[1,50],[0.5,25],[2,29]</t>
@@ -1397,7 +1487,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="8" max="8" width="19.7809523809524" customWidth="1"/>
@@ -1405,9 +1495,9 @@
     <col min="10" max="10" width="19.8857142857143" customWidth="1"/>
     <col min="11" max="11" width="21.552380952381" customWidth="1"/>
     <col min="12" max="12" width="20.1142857142857" customWidth="1"/>
-    <col min="13" max="13" width="21.7809523809524" customWidth="1"/>
-    <col min="14" max="14" width="17.4285714285714" customWidth="1"/>
-    <col min="15" max="15" width="20.7142857142857" customWidth="1"/>
+    <col min="13" max="14" width="21.7809523809524" customWidth="1"/>
+    <col min="15" max="15" width="17.4285714285714" customWidth="1"/>
+    <col min="16" max="16" width="20.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1418,7 +1508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:24">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1482,138 +1572,153 @@
       <c r="V2" t="s">
         <v>21</v>
       </c>
+      <c r="W2" t="s">
+        <v>22</v>
+      </c>
+      <c r="X2" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:24">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="P3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="R3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="S3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="T3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="U3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="V3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="W3" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="X3" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:24">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="V4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="R4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>42</v>
+      <c r="X4" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="5" spans="2:22">
+    <row r="5" spans="2:24">
       <c r="B5">
         <v>1</v>
       </c>
@@ -1642,40 +1747,46 @@
         <v>60</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
       <c r="N5" t="s">
-        <v>43</v>
-      </c>
-      <c r="O5">
+        <v>45</v>
+      </c>
+      <c r="O5" t="s">
+        <v>46</v>
+      </c>
+      <c r="P5">
         <v>100</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
+        <v>10</v>
+      </c>
+      <c r="R5">
+        <v>2</v>
+      </c>
+      <c r="S5">
+        <v>1000</v>
+      </c>
+      <c r="T5">
+        <v>4</v>
+      </c>
+      <c r="U5">
+        <v>100</v>
+      </c>
+      <c r="V5" t="s">
+        <v>45</v>
+      </c>
+      <c r="W5" t="s">
+        <v>46</v>
+      </c>
+      <c r="X5">
         <v>0</v>
       </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>1000</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" spans="2:22">
+    <row r="6" spans="2:24">
       <c r="B6">
         <v>2</v>
       </c>
@@ -1704,28 +1815,28 @@
         <v>60</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M6">
         <v>50</v>
       </c>
       <c r="N6" t="s">
-        <v>44</v>
-      </c>
-      <c r="O6">
+        <v>47</v>
+      </c>
+      <c r="O6" t="s">
+        <v>48</v>
+      </c>
+      <c r="P6">
         <v>100</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
       </c>
       <c r="Q6">
         <v>0</v>
       </c>
       <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
         <v>2000</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
       </c>
       <c r="T6">
         <v>0</v>
@@ -1733,11 +1844,17 @@
       <c r="U6">
         <v>0</v>
       </c>
-      <c r="V6">
-        <v>0</v>
+      <c r="V6" t="s">
+        <v>47</v>
+      </c>
+      <c r="W6" t="s">
+        <v>48</v>
+      </c>
+      <c r="X6">
+        <v>100</v>
       </c>
     </row>
-    <row r="7" spans="2:22">
+    <row r="7" spans="2:24">
       <c r="B7">
         <v>3</v>
       </c>
@@ -1766,40 +1883,46 @@
         <v>60</v>
       </c>
       <c r="L7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M7">
         <v>50</v>
       </c>
       <c r="N7" t="s">
-        <v>45</v>
-      </c>
-      <c r="O7">
+        <v>49</v>
+      </c>
+      <c r="O7" t="s">
         <v>50</v>
       </c>
       <c r="P7">
+        <v>50</v>
+      </c>
+      <c r="Q7">
         <v>10</v>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <v>2</v>
       </c>
-      <c r="R7">
+      <c r="S7">
         <v>4000</v>
       </c>
-      <c r="S7">
-        <v>2</v>
-      </c>
       <c r="T7">
+        <v>4</v>
+      </c>
+      <c r="U7">
         <v>50</v>
       </c>
-      <c r="U7">
-        <v>2</v>
-      </c>
-      <c r="V7">
+      <c r="V7" t="s">
+        <v>49</v>
+      </c>
+      <c r="W7" t="s">
         <v>50</v>
       </c>
+      <c r="X7">
+        <v>50</v>
+      </c>
     </row>
-    <row r="8" spans="2:22">
+    <row r="8" spans="2:24">
       <c r="B8">
         <v>4</v>
       </c>
@@ -1828,40 +1951,46 @@
         <v>60</v>
       </c>
       <c r="L8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M8">
         <v>50</v>
       </c>
       <c r="N8" t="s">
-        <v>46</v>
-      </c>
-      <c r="O8">
+        <v>51</v>
+      </c>
+      <c r="O8" t="s">
+        <v>52</v>
+      </c>
+      <c r="P8">
         <v>50</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>20</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <v>3</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <v>8000</v>
       </c>
-      <c r="S8">
-        <v>2</v>
-      </c>
       <c r="T8">
+        <v>4</v>
+      </c>
+      <c r="U8">
         <v>50</v>
       </c>
-      <c r="U8">
-        <v>2</v>
-      </c>
-      <c r="V8">
+      <c r="V8" t="s">
+        <v>51</v>
+      </c>
+      <c r="W8" t="s">
+        <v>52</v>
+      </c>
+      <c r="X8">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="2:22">
+    <row r="9" spans="2:24">
       <c r="B9">
         <v>5</v>
       </c>
@@ -1890,36 +2019,42 @@
         <v>60</v>
       </c>
       <c r="L9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M9">
         <v>50</v>
       </c>
       <c r="N9" t="s">
-        <v>47</v>
-      </c>
-      <c r="O9">
+        <v>53</v>
+      </c>
+      <c r="O9" t="s">
+        <v>54</v>
+      </c>
+      <c r="P9">
         <v>50</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>30</v>
       </c>
-      <c r="Q9">
+      <c r="R9">
         <v>4</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <v>16000</v>
       </c>
-      <c r="S9">
-        <v>2</v>
-      </c>
       <c r="T9">
+        <v>4</v>
+      </c>
+      <c r="U9">
         <v>50</v>
       </c>
-      <c r="U9">
-        <v>2</v>
-      </c>
-      <c r="V9">
+      <c r="V9" t="s">
+        <v>53</v>
+      </c>
+      <c r="W9" t="s">
+        <v>54</v>
+      </c>
+      <c r="X9">
         <v>50</v>
       </c>
     </row>

--- a/GF_X-master/AAAGameData/DataTables/Level1SettingTable.xlsx
+++ b/GF_X-master/AAAGameData/DataTables/Level1SettingTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowHeight="17925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -1498,6 +1498,8 @@
     <col min="13" max="14" width="21.7809523809524" customWidth="1"/>
     <col min="15" max="15" width="17.4285714285714" customWidth="1"/>
     <col min="16" max="16" width="20.7142857142857" customWidth="1"/>
+    <col min="23" max="23" width="15.8571428571429" customWidth="1"/>
+    <col min="24" max="24" width="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1726,7 +1728,7 @@
         <v>2400</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -1759,7 +1761,7 @@
         <v>46</v>
       </c>
       <c r="P5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q5">
         <v>10</v>
@@ -1774,7 +1776,7 @@
         <v>4</v>
       </c>
       <c r="U5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V5" t="s">
         <v>45</v>
@@ -1794,7 +1796,7 @@
         <v>4800</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F6">
         <v>4</v>
@@ -1827,7 +1829,7 @@
         <v>48</v>
       </c>
       <c r="P6">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1851,7 +1853,7 @@
         <v>48</v>
       </c>
       <c r="X6">
-        <v>100</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="2:24">
@@ -1862,7 +1864,7 @@
         <v>9600</v>
       </c>
       <c r="E7">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -1895,7 +1897,7 @@
         <v>50</v>
       </c>
       <c r="P7">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="Q7">
         <v>10</v>
@@ -1919,7 +1921,7 @@
         <v>50</v>
       </c>
       <c r="X7">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="2:24">
@@ -1930,7 +1932,7 @@
         <v>19200</v>
       </c>
       <c r="E8">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="F8">
         <v>8</v>
@@ -1963,7 +1965,7 @@
         <v>52</v>
       </c>
       <c r="P8">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="Q8">
         <v>20</v>
@@ -1987,7 +1989,7 @@
         <v>52</v>
       </c>
       <c r="X8">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="2:24">
@@ -1998,7 +2000,7 @@
         <v>38400</v>
       </c>
       <c r="E9">
-        <v>160</v>
+        <v>400</v>
       </c>
       <c r="F9">
         <v>10</v>
@@ -2031,7 +2033,7 @@
         <v>54</v>
       </c>
       <c r="P9">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q9">
         <v>30</v>
@@ -2055,7 +2057,7 @@
         <v>54</v>
       </c>
       <c r="X9">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/GF_X-master/AAAGameData/DataTables/Level1SettingTable.xlsx
+++ b/GF_X-master/AAAGameData/DataTables/Level1SettingTable.xlsx
@@ -1764,10 +1764,10 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="R5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S5">
         <v>1000</v>
@@ -1832,10 +1832,10 @@
         <v>70</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S6">
         <v>2000</v>
@@ -1900,10 +1900,10 @@
         <v>70</v>
       </c>
       <c r="Q7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S7">
         <v>4000</v>
@@ -1968,7 +1968,7 @@
         <v>70</v>
       </c>
       <c r="Q8">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>3</v>
@@ -2036,10 +2036,10 @@
         <v>60</v>
       </c>
       <c r="Q9">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="R9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S9">
         <v>16000</v>

--- a/GF_X-master/AAAGameData/DataTables/Level1SettingTable.xlsx
+++ b/GF_X-master/AAAGameData/DataTables/Level1SettingTable.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17925"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -129,7 +130,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="55">
   <si>
     <t>#</t>
   </si>
@@ -1229,6 +1230,949 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="zh-CN" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$D$8:$D$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$E$8:$E$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$F$8:$F$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4500</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>32000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="414090821"/>
+        <c:axId val="594897190"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="414090821"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="594897190"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="594897190"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="414090821"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
+        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{476f21e6-d703-4d32-9848-670d7b1879bd}"/>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="zh-CN"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>109220</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>58420</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="图表 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="4376420" y="858520"/>
+        <a:ext cx="4826000" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
@@ -1487,18 +2431,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:X10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="8" max="8" width="19.7809523809524" customWidth="1"/>
-    <col min="9" max="9" width="21.447619047619" customWidth="1"/>
-    <col min="10" max="10" width="19.8857142857143" customWidth="1"/>
-    <col min="11" max="11" width="21.552380952381" customWidth="1"/>
-    <col min="12" max="12" width="20.1142857142857" customWidth="1"/>
-    <col min="13" max="14" width="21.7809523809524" customWidth="1"/>
-    <col min="15" max="15" width="17.4285714285714" customWidth="1"/>
-    <col min="16" max="16" width="20.7142857142857" customWidth="1"/>
-    <col min="23" max="23" width="15.8571428571429" customWidth="1"/>
+    <col min="8" max="8" width="19.7777777777778" customWidth="1"/>
+    <col min="9" max="9" width="21.4444444444444" customWidth="1"/>
+    <col min="10" max="10" width="19.8888888888889" customWidth="1"/>
+    <col min="11" max="11" width="21.5555555555556" customWidth="1"/>
+    <col min="12" max="12" width="20.1111111111111" customWidth="1"/>
+    <col min="13" max="14" width="21.7777777777778" customWidth="1"/>
+    <col min="15" max="15" width="17.4259259259259" customWidth="1"/>
+    <col min="16" max="16" width="20.712962962963" customWidth="1"/>
+    <col min="23" max="23" width="15.8611111111111" customWidth="1"/>
     <col min="24" max="24" width="19" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1725,7 +2669,7 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>2400</v>
+        <v>1000</v>
       </c>
       <c r="E5">
         <v>25</v>
@@ -1737,16 +2681,16 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J5">
         <v>2</v>
       </c>
       <c r="K5">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L5">
         <v>4</v>
@@ -1773,7 +2717,7 @@
         <v>1000</v>
       </c>
       <c r="T5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U5">
         <v>0</v>
@@ -1785,7 +2729,7 @@
         <v>46</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="2:24">
@@ -1793,7 +2737,7 @@
         <v>2</v>
       </c>
       <c r="D6">
-        <v>4800</v>
+        <v>4500</v>
       </c>
       <c r="E6">
         <v>50</v>
@@ -1805,16 +2749,16 @@
         <v>1</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>50</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L6">
         <v>4</v>
@@ -1832,7 +2776,7 @@
         <v>70</v>
       </c>
       <c r="Q6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>4</v>
@@ -1861,7 +2805,7 @@
         <v>3</v>
       </c>
       <c r="D7">
-        <v>9600</v>
+        <v>9000</v>
       </c>
       <c r="E7">
         <v>100</v>
@@ -1873,16 +2817,16 @@
         <v>2</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>50</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L7">
         <v>4</v>
@@ -1900,10 +2844,10 @@
         <v>70</v>
       </c>
       <c r="Q7">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="R7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S7">
         <v>4000</v>
@@ -1929,7 +2873,7 @@
         <v>4</v>
       </c>
       <c r="D8">
-        <v>19200</v>
+        <v>16000</v>
       </c>
       <c r="E8">
         <v>200</v>
@@ -1941,19 +2885,19 @@
         <v>3</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I8">
         <v>50</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K8">
         <v>60</v>
       </c>
       <c r="L8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M8">
         <v>50</v>
@@ -1968,13 +2912,13 @@
         <v>70</v>
       </c>
       <c r="Q8">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R8">
         <v>3</v>
       </c>
       <c r="S8">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="T8">
         <v>4</v>
@@ -1997,7 +2941,7 @@
         <v>5</v>
       </c>
       <c r="D9">
-        <v>38400</v>
+        <v>32000</v>
       </c>
       <c r="E9">
         <v>400</v>
@@ -2009,19 +2953,19 @@
         <v>4</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>50</v>
       </c>
       <c r="J9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K9">
         <v>60</v>
       </c>
       <c r="L9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M9">
         <v>50</v>
@@ -2057,6 +3001,74 @@
         <v>54</v>
       </c>
       <c r="X9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="2:24">
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="D10">
+        <v>100</v>
+      </c>
+      <c r="E10">
+        <v>400</v>
+      </c>
+      <c r="F10">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>4</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <v>50</v>
+      </c>
+      <c r="J10">
+        <v>4</v>
+      </c>
+      <c r="K10">
+        <v>60</v>
+      </c>
+      <c r="L10">
+        <v>3</v>
+      </c>
+      <c r="M10">
+        <v>50</v>
+      </c>
+      <c r="N10" t="s">
+        <v>53</v>
+      </c>
+      <c r="O10" t="s">
+        <v>54</v>
+      </c>
+      <c r="P10">
+        <v>60</v>
+      </c>
+      <c r="Q10">
+        <v>20</v>
+      </c>
+      <c r="R10">
+        <v>3</v>
+      </c>
+      <c r="S10">
+        <v>16000</v>
+      </c>
+      <c r="T10">
+        <v>4</v>
+      </c>
+      <c r="U10">
+        <v>50</v>
+      </c>
+      <c r="V10" t="s">
+        <v>53</v>
+      </c>
+      <c r="W10" t="s">
+        <v>54</v>
+      </c>
+      <c r="X10">
         <v>60</v>
       </c>
     </row>
@@ -2073,4 +3085,57 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="D8:F12"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetData>
+    <row r="8" spans="4:6">
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="9" spans="4:6">
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="10" spans="4:6">
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="F10">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="11" spans="4:6">
+      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="F11">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="12" spans="4:6">
+      <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="F12">
+        <v>32000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/GF_X-master/AAAGameData/DataTables/Level1SettingTable.xlsx
+++ b/GF_X-master/AAAGameData/DataTables/Level1SettingTable.xlsx
@@ -1300,97 +1300,24 @@
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>Sheet3!$D$8:$D$12</c:f>
+              <c:f>Sheet3!$H$8:$H$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>136</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet3!$E$8:$E$12</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet3!$F$8:$F$12</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>1000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4500</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>16000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>32000</c:v>
+                  <c:v>160</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2142,16 +2069,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>109220</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>238760</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>58420</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>187960</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2159,7 +2086,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4376420" y="858520"/>
+        <a:off x="5999480" y="896620"/>
         <a:ext cx="4826000" cy="2743200"/>
       </xdr:xfrm>
       <a:graphic>
@@ -2672,7 +2599,7 @@
         <v>1000</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -2681,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J5">
         <v>2</v>
@@ -2737,16 +2664,16 @@
         <v>2</v>
       </c>
       <c r="D6">
-        <v>4500</v>
+        <v>4800</v>
       </c>
       <c r="E6">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F6">
         <v>4</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6">
         <v>3</v>
@@ -2755,7 +2682,7 @@
         <v>50</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K6">
         <v>50</v>
@@ -2776,7 +2703,7 @@
         <v>70</v>
       </c>
       <c r="Q6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R6">
         <v>4</v>
@@ -2805,7 +2732,7 @@
         <v>3</v>
       </c>
       <c r="D7">
-        <v>9000</v>
+        <v>13600</v>
       </c>
       <c r="E7">
         <v>100</v>
@@ -2814,7 +2741,7 @@
         <v>6</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7">
         <v>5</v>
@@ -2873,10 +2800,10 @@
         <v>4</v>
       </c>
       <c r="D8">
-        <v>16000</v>
+        <v>22500</v>
       </c>
       <c r="E8">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F8">
         <v>8</v>
@@ -2941,10 +2868,10 @@
         <v>5</v>
       </c>
       <c r="D9">
-        <v>32000</v>
+        <v>48000</v>
       </c>
       <c r="E9">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F9">
         <v>10</v>
@@ -3018,7 +2945,7 @@
         <v>10</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <v>5</v>
@@ -3090,47 +3017,100 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="D8:F12"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="D8:H13"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="8" max="8" width="12.8888888888889"/>
+  </cols>
   <sheetData>
-    <row r="8" spans="4:6">
+    <row r="8" spans="4:8">
       <c r="D8">
         <v>1</v>
       </c>
       <c r="F8">
         <v>1000</v>
       </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <f t="shared" ref="H8:H13" si="0">F8/G8</f>
+        <v>100</v>
+      </c>
     </row>
-    <row r="9" spans="4:6">
+    <row r="9" spans="4:8">
       <c r="D9">
         <v>2</v>
       </c>
       <c r="F9">
-        <v>4500</v>
+        <v>4800</v>
+      </c>
+      <c r="G9">
+        <v>40</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>120</v>
       </c>
     </row>
-    <row r="10" spans="4:6">
+    <row r="10" spans="4:8">
       <c r="D10">
         <v>3</v>
       </c>
       <c r="F10">
-        <v>9000</v>
+        <v>13600</v>
+      </c>
+      <c r="G10">
+        <v>100</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>136</v>
       </c>
     </row>
-    <row r="11" spans="4:6">
+    <row r="11" spans="4:8">
       <c r="D11">
         <v>4</v>
       </c>
       <c r="F11">
-        <v>16000</v>
+        <v>22500</v>
+      </c>
+      <c r="G11">
+        <v>150</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>150</v>
       </c>
     </row>
-    <row r="12" spans="4:6">
+    <row r="12" spans="4:8">
       <c r="D12">
         <v>5</v>
       </c>
       <c r="F12">
-        <v>32000</v>
+        <v>48000</v>
+      </c>
+      <c r="G12">
+        <v>300</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="13" spans="4:8">
+      <c r="D13">
+        <v>6</v>
+      </c>
+      <c r="F13">
+        <v>100</v>
+      </c>
+      <c r="G13">
+        <v>400</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>

--- a/GF_X-master/AAAGameData/DataTables/Level1SettingTable.xlsx
+++ b/GF_X-master/AAAGameData/DataTables/Level1SettingTable.xlsx
@@ -2602,7 +2602,7 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -2670,10 +2670,10 @@
         <v>40</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>3</v>
@@ -2738,10 +2738,10 @@
         <v>100</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7">
         <v>5</v>
@@ -2806,7 +2806,7 @@
         <v>150</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G8">
         <v>3</v>
